--- a/services/data_raw/eurostat/AT_coal_NRG_CB_SFFM.xlsx
+++ b/services/data_raw/eurostat/AT_coal_NRG_CB_SFFM.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,1108 +413,1118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HL50"/>
+  <dimension ref="A1:HN50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>freq</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>nrg_bal</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>siec</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>geo\TIME_PERIOD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>2008-01</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>2008-02</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>2008-03</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>2008-04</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2008-05</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>2008-06</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>2008-07</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>2008-08</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>2008-09</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>2008-10</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>2008-11</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>2008-12</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>2009-01</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>2009-02</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>2009-03</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>2009-04</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>2009-05</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>2009-06</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>2009-07</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>2009-08</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>2009-09</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>2009-10</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>2009-11</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>2009-12</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>2010-01</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>2010-02</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>2010-03</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>2010-04</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>2010-05</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>2010-06</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>2010-07</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>2010-08</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>2010-09</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>2010-10</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>2010-11</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>2010-12</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>2011-01</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>2011-02</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>2011-03</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>2011-04</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>2011-05</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>2011-06</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>2011-07</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>2011-08</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>2011-09</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>2011-10</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>2011-11</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>2011-12</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>2012-01</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>2012-02</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>2012-03</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>2012-04</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>2012-05</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>2012-06</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>2012-07</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>2012-08</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>2012-09</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>2012-10</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>2012-11</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>2012-12</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>2013-01</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>2013-02</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>2013-03</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>2013-04</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>2013-05</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>2013-06</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>2013-07</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>2013-08</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>2013-09</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>2013-10</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>2013-11</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>2013-12</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>2014-01</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>2014-02</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>2014-03</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>2014-04</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>2014-05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>2014-06</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>2014-07</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>2014-09</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>2014-10</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>2014-11</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>2014-12</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>2015-01</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>2015-02</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>2015-03</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>2015-04</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>2015-05</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>2015-06</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>2015-07</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>2015-09</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>2015-10</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>2015-11</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>2015-12</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>2016-01</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>2016-02</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>2016-03</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>2016-04</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>2016-05</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>2016-06</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>2016-07</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>2016-08</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>2016-09</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>2016-10</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>2016-11</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>2016-12</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>2017-01</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>2017-02</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>2017-03</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>2017-04</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>2017-05</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>2017-06</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>2017-07</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>2017-08</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>2017-09</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>2017-10</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>2017-11</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>2017-12</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>2018-01</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>2018-02</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>2018-03</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>2018-04</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>2018-05</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>2018-06</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>2018-07</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>2018-08</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>2018-09</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>2018-10</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>2018-11</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>2018-12</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>2019-01</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>2019-02</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>2019-03</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>2019-04</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>2019-05</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>2019-06</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>2019-07</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>2019-08</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>2019-09</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>2019-10</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>2019-11</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>2019-12</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>2020-01</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>2020-02</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>2020-03</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>2020-04</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>2020-05</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>2020-06</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>2020-07</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>2020-08</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>2020-09</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>2020-10</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>2020-11</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>2020-12</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FG1" t="inlineStr">
         <is>
           <t>2021-01</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>2021-02</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>2021-03</t>
         </is>
       </c>
-      <c r="FJ1" s="1" t="inlineStr">
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>2021-04</t>
         </is>
       </c>
-      <c r="FK1" s="1" t="inlineStr">
+      <c r="FK1" t="inlineStr">
         <is>
           <t>2021-05</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FL1" t="inlineStr">
         <is>
           <t>2021-06</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="FM1" t="inlineStr">
         <is>
           <t>2021-07</t>
         </is>
       </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="FN1" t="inlineStr">
         <is>
           <t>2021-08</t>
         </is>
       </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FO1" t="inlineStr">
         <is>
           <t>2021-09</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FP1" t="inlineStr">
         <is>
           <t>2021-10</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FQ1" t="inlineStr">
         <is>
           <t>2021-11</t>
         </is>
       </c>
-      <c r="FR1" s="1" t="inlineStr">
+      <c r="FR1" t="inlineStr">
         <is>
           <t>2021-12</t>
         </is>
       </c>
-      <c r="FS1" s="1" t="inlineStr">
+      <c r="FS1" t="inlineStr">
         <is>
           <t>2022-01</t>
         </is>
       </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FT1" t="inlineStr">
         <is>
           <t>2022-02</t>
         </is>
       </c>
-      <c r="FU1" s="1" t="inlineStr">
+      <c r="FU1" t="inlineStr">
         <is>
           <t>2022-03</t>
         </is>
       </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FV1" t="inlineStr">
         <is>
           <t>2022-04</t>
         </is>
       </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="FW1" t="inlineStr">
         <is>
           <t>2022-05</t>
         </is>
       </c>
-      <c r="FX1" s="1" t="inlineStr">
+      <c r="FX1" t="inlineStr">
         <is>
           <t>2022-06</t>
         </is>
       </c>
-      <c r="FY1" s="1" t="inlineStr">
+      <c r="FY1" t="inlineStr">
         <is>
           <t>2022-07</t>
         </is>
       </c>
-      <c r="FZ1" s="1" t="inlineStr">
+      <c r="FZ1" t="inlineStr">
         <is>
           <t>2022-08</t>
         </is>
       </c>
-      <c r="GA1" s="1" t="inlineStr">
+      <c r="GA1" t="inlineStr">
         <is>
           <t>2022-09</t>
         </is>
       </c>
-      <c r="GB1" s="1" t="inlineStr">
+      <c r="GB1" t="inlineStr">
         <is>
           <t>2022-10</t>
         </is>
       </c>
-      <c r="GC1" s="1" t="inlineStr">
+      <c r="GC1" t="inlineStr">
         <is>
           <t>2022-11</t>
         </is>
       </c>
-      <c r="GD1" s="1" t="inlineStr">
+      <c r="GD1" t="inlineStr">
         <is>
           <t>2022-12</t>
         </is>
       </c>
-      <c r="GE1" s="1" t="inlineStr">
+      <c r="GE1" t="inlineStr">
         <is>
           <t>2023-01</t>
         </is>
       </c>
-      <c r="GF1" s="1" t="inlineStr">
+      <c r="GF1" t="inlineStr">
         <is>
           <t>2023-02</t>
         </is>
       </c>
-      <c r="GG1" s="1" t="inlineStr">
+      <c r="GG1" t="inlineStr">
         <is>
           <t>2023-03</t>
         </is>
       </c>
-      <c r="GH1" s="1" t="inlineStr">
+      <c r="GH1" t="inlineStr">
         <is>
           <t>2023-04</t>
         </is>
       </c>
-      <c r="GI1" s="1" t="inlineStr">
+      <c r="GI1" t="inlineStr">
         <is>
           <t>2023-05</t>
         </is>
       </c>
-      <c r="GJ1" s="1" t="inlineStr">
+      <c r="GJ1" t="inlineStr">
         <is>
           <t>2023-06</t>
         </is>
       </c>
-      <c r="GK1" s="1" t="inlineStr">
+      <c r="GK1" t="inlineStr">
         <is>
           <t>2023-07</t>
         </is>
       </c>
-      <c r="GL1" s="1" t="inlineStr">
+      <c r="GL1" t="inlineStr">
         <is>
           <t>2023-08</t>
         </is>
       </c>
-      <c r="GM1" s="1" t="inlineStr">
+      <c r="GM1" t="inlineStr">
         <is>
           <t>2023-09</t>
         </is>
       </c>
-      <c r="GN1" s="1" t="inlineStr">
+      <c r="GN1" t="inlineStr">
         <is>
           <t>2023-10</t>
         </is>
       </c>
-      <c r="GO1" s="1" t="inlineStr">
+      <c r="GO1" t="inlineStr">
         <is>
           <t>2023-11</t>
         </is>
       </c>
-      <c r="GP1" s="1" t="inlineStr">
+      <c r="GP1" t="inlineStr">
         <is>
           <t>2023-12</t>
         </is>
       </c>
-      <c r="GQ1" s="1" t="inlineStr">
+      <c r="GQ1" t="inlineStr">
         <is>
           <t>2024-01</t>
         </is>
       </c>
-      <c r="GR1" s="1" t="inlineStr">
+      <c r="GR1" t="inlineStr">
         <is>
           <t>2024-02</t>
         </is>
       </c>
-      <c r="GS1" s="1" t="inlineStr">
+      <c r="GS1" t="inlineStr">
         <is>
           <t>2024-03</t>
         </is>
       </c>
-      <c r="GT1" s="1" t="inlineStr">
+      <c r="GT1" t="inlineStr">
         <is>
           <t>2024-04</t>
         </is>
       </c>
-      <c r="GU1" s="1" t="inlineStr">
+      <c r="GU1" t="inlineStr">
         <is>
           <t>2024-05</t>
         </is>
       </c>
-      <c r="GV1" s="1" t="inlineStr">
+      <c r="GV1" t="inlineStr">
         <is>
           <t>2024-06</t>
         </is>
       </c>
-      <c r="GW1" s="1" t="inlineStr">
+      <c r="GW1" t="inlineStr">
         <is>
           <t>2024-07</t>
         </is>
       </c>
-      <c r="GX1" s="1" t="inlineStr">
+      <c r="GX1" t="inlineStr">
         <is>
           <t>2024-08</t>
         </is>
       </c>
-      <c r="GY1" s="1" t="inlineStr">
+      <c r="GY1" t="inlineStr">
         <is>
           <t>2024-09</t>
         </is>
       </c>
-      <c r="GZ1" s="1" t="inlineStr">
+      <c r="GZ1" t="inlineStr">
         <is>
           <t>2024-10</t>
         </is>
       </c>
-      <c r="HA1" s="1" t="inlineStr">
+      <c r="HA1" t="inlineStr">
         <is>
           <t>2024-11</t>
         </is>
       </c>
-      <c r="HB1" s="1" t="inlineStr">
+      <c r="HB1" t="inlineStr">
         <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="HC1" s="1" t="inlineStr">
+      <c r="HC1" t="inlineStr">
         <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="HD1" s="1" t="inlineStr">
+      <c r="HD1" t="inlineStr">
         <is>
           <t>2025-02</t>
         </is>
       </c>
-      <c r="HE1" s="1" t="inlineStr">
+      <c r="HE1" t="inlineStr">
         <is>
           <t>2025-03</t>
         </is>
       </c>
-      <c r="HF1" s="1" t="inlineStr">
+      <c r="HF1" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="HG1" s="1" t="inlineStr">
+      <c r="HG1" t="inlineStr">
         <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="HH1" s="1" t="inlineStr">
+      <c r="HH1" t="inlineStr">
         <is>
           <t>2025-06</t>
         </is>
       </c>
-      <c r="HI1" s="1" t="inlineStr">
+      <c r="HI1" t="inlineStr">
         <is>
           <t>2025-07</t>
         </is>
       </c>
-      <c r="HJ1" s="1" t="inlineStr">
+      <c r="HJ1" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
       </c>
-      <c r="HK1" s="1" t="inlineStr">
+      <c r="HK1" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="HL1" s="1" t="inlineStr">
+      <c r="HL1" t="inlineStr">
         <is>
           <t>2025-10</t>
+        </is>
+      </c>
+      <c r="HM1" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="HN1" t="inlineStr">
+        <is>
+          <t>2025-12</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -2194,11 +2192,17 @@
         <v>0</v>
       </c>
       <c r="HL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -2866,11 +2870,17 @@
         <v>0</v>
       </c>
       <c r="HL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -3540,9 +3550,15 @@
       <c r="HL4" t="n">
         <v>183.682</v>
       </c>
+      <c r="HM4" t="n">
+        <v>209.061</v>
+      </c>
+      <c r="HN4" t="n">
+        <v>177.923</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -3996,9 +4012,15 @@
       <c r="HL5" t="n">
         <v>79.32599999999999</v>
       </c>
+      <c r="HM5" t="n">
+        <v>109.68</v>
+      </c>
+      <c r="HN5" t="n">
+        <v>118.64</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -4666,11 +4688,17 @@
         <v>0</v>
       </c>
       <c r="HL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -5340,9 +5368,15 @@
       <c r="HL7" t="n">
         <v>291.567</v>
       </c>
+      <c r="HM7" t="n">
+        <v>262.673</v>
+      </c>
+      <c r="HN7" t="n">
+        <v>278.733</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -6012,9 +6046,15 @@
       <c r="HL8" t="n">
         <v>262.673</v>
       </c>
+      <c r="HM8" t="n">
+        <v>278.733</v>
+      </c>
+      <c r="HN8" t="n">
+        <v>252.838</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -6684,9 +6724,15 @@
       <c r="HL9" t="n">
         <v>28.894</v>
       </c>
+      <c r="HM9" t="n">
+        <v>-16.06</v>
+      </c>
+      <c r="HN9" t="n">
+        <v>25.895</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -7356,9 +7402,15 @@
       <c r="HL10" t="n">
         <v>212.576</v>
       </c>
+      <c r="HM10" t="n">
+        <v>193</v>
+      </c>
+      <c r="HN10" t="n">
+        <v>203.819</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -7812,9 +7864,15 @@
       <c r="HL11" t="n">
         <v>211.103</v>
       </c>
+      <c r="HM11" t="n">
+        <v>189.256</v>
+      </c>
+      <c r="HN11" t="n">
+        <v>200.074</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -8484,9 +8542,15 @@
       <c r="HL12" t="n">
         <v>0</v>
       </c>
+      <c r="HM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -9156,9 +9220,15 @@
       <c r="HL13" t="n">
         <v>143.837</v>
       </c>
+      <c r="HM13" t="n">
+        <v>139.01</v>
+      </c>
+      <c r="HN13" t="n">
+        <v>139.961</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -9828,9 +9898,15 @@
       <c r="HL14" t="n">
         <v>67.065</v>
       </c>
+      <c r="HM14" t="n">
+        <v>50.046</v>
+      </c>
+      <c r="HN14" t="n">
+        <v>59.913</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -10284,9 +10360,15 @@
       <c r="HL15" t="n">
         <v>67.065</v>
       </c>
+      <c r="HM15" t="n">
+        <v>50.046</v>
+      </c>
+      <c r="HN15" t="n">
+        <v>59.913</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -10956,9 +11038,15 @@
       <c r="HL16" t="n">
         <v>0.2</v>
       </c>
+      <c r="HM16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="HN16" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -11412,9 +11500,15 @@
       <c r="HL17" t="n">
         <v>1.473</v>
       </c>
+      <c r="HM17" t="n">
+        <v>3.745</v>
+      </c>
+      <c r="HN17" t="n">
+        <v>3.745</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -12082,11 +12176,17 @@
         <v>0</v>
       </c>
       <c r="HL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -12756,9 +12856,15 @@
       <c r="HL19" t="n">
         <v>4.9</v>
       </c>
+      <c r="HM19" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="HN19" t="n">
+        <v>4.029</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -13426,11 +13532,17 @@
         <v>0</v>
       </c>
       <c r="HL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -14098,11 +14210,17 @@
         <v>0</v>
       </c>
       <c r="HL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -14770,11 +14888,17 @@
         <v>0</v>
       </c>
       <c r="HL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -15442,11 +15566,17 @@
         <v>0</v>
       </c>
       <c r="HL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -16116,9 +16246,15 @@
       <c r="HL24" t="n">
         <v>4.9</v>
       </c>
+      <c r="HM24" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="HN24" t="n">
+        <v>4.029</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -16786,11 +16922,17 @@
         <v>0</v>
       </c>
       <c r="HL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -17460,9 +17602,15 @@
       <c r="HL26" t="n">
         <v>106.083</v>
       </c>
+      <c r="HM26" t="n">
+        <v>102.624</v>
+      </c>
+      <c r="HN26" t="n">
+        <v>107.81</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -18132,9 +18280,15 @@
       <c r="HL27" t="n">
         <v>87.958</v>
       </c>
+      <c r="HM27" t="n">
+        <v>72.91500000000001</v>
+      </c>
+      <c r="HN27" t="n">
+        <v>103.114</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -18588,9 +18742,15 @@
       <c r="HL28" t="n">
         <v>0</v>
       </c>
+      <c r="HM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -19260,9 +19420,15 @@
       <c r="HL29" t="n">
         <v>0</v>
       </c>
+      <c r="HM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -19932,9 +20098,15 @@
       <c r="HL30" t="n">
         <v>60.861</v>
       </c>
+      <c r="HM30" t="n">
+        <v>48.516</v>
+      </c>
+      <c r="HN30" t="n">
+        <v>46.113</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -20604,9 +20776,15 @@
       <c r="HL31" t="n">
         <v>48.516</v>
       </c>
+      <c r="HM31" t="n">
+        <v>46.113</v>
+      </c>
+      <c r="HN31" t="n">
+        <v>70.413</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -21276,9 +21454,15 @@
       <c r="HL32" t="n">
         <v>12.345</v>
       </c>
+      <c r="HM32" t="n">
+        <v>2.403</v>
+      </c>
+      <c r="HN32" t="n">
+        <v>-24.3</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>31</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -21948,9 +22132,15 @@
       <c r="HL33" t="n">
         <v>206.386</v>
       </c>
+      <c r="HM33" t="n">
+        <v>177.942</v>
+      </c>
+      <c r="HN33" t="n">
+        <v>186.624</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>32</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -22620,9 +22810,15 @@
       <c r="HL34" t="n">
         <v>200.339</v>
       </c>
+      <c r="HM34" t="n">
+        <v>173.852</v>
+      </c>
+      <c r="HN34" t="n">
+        <v>182.503</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>33</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -23290,11 +23486,17 @@
         <v>0</v>
       </c>
       <c r="HL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>34</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -23964,9 +24166,15 @@
       <c r="HL36" t="n">
         <v>0</v>
       </c>
+      <c r="HM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>35</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -24634,11 +24842,17 @@
         <v>0</v>
       </c>
       <c r="HL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>36</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -25096,9 +25310,11 @@
       <c r="HJ38" t="inlineStr"/>
       <c r="HK38" t="inlineStr"/>
       <c r="HL38" t="inlineStr"/>
+      <c r="HM38" t="inlineStr"/>
+      <c r="HN38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>37</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -25556,9 +25772,11 @@
       <c r="HJ39" t="inlineStr"/>
       <c r="HK39" t="inlineStr"/>
       <c r="HL39" t="inlineStr"/>
+      <c r="HM39" t="inlineStr"/>
+      <c r="HN39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>38</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -26226,11 +26444,17 @@
         <v>0</v>
       </c>
       <c r="HL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN40" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>39</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -26900,9 +27124,15 @@
       <c r="HL41" t="n">
         <v>0</v>
       </c>
+      <c r="HM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" t="n">
         <v>40</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -27570,11 +27800,17 @@
         <v>0</v>
       </c>
       <c r="HL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" t="n">
         <v>41</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -28028,9 +28264,15 @@
       <c r="HL43" t="n">
         <v>0</v>
       </c>
+      <c r="HM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" t="n">
         <v>42</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -28484,9 +28726,15 @@
       <c r="HL44" t="n">
         <v>0</v>
       </c>
+      <c r="HM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" t="n">
         <v>43</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -28940,9 +29188,15 @@
       <c r="HL45" t="n">
         <v>0</v>
       </c>
+      <c r="HM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" t="n">
         <v>44</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -29396,9 +29650,15 @@
       <c r="HL46" t="n">
         <v>0</v>
       </c>
+      <c r="HM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" t="n">
         <v>45</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -29852,9 +30112,15 @@
       <c r="HL47" t="n">
         <v>0</v>
       </c>
+      <c r="HM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" t="n">
         <v>46</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -30308,9 +30574,15 @@
       <c r="HL48" t="n">
         <v>0</v>
       </c>
+      <c r="HM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" t="n">
         <v>47</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -30764,9 +31036,15 @@
       <c r="HL49" t="n">
         <v>0</v>
       </c>
+      <c r="HM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" t="n">
         <v>48</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -31220,6 +31498,12 @@
       <c r="HL50" t="n">
         <v>0</v>
       </c>
+      <c r="HM50" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN50" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/services/data_raw/eurostat/AT_coal_NRG_CB_SFFM.xlsx
+++ b/services/data_raw/eurostat/AT_coal_NRG_CB_SFFM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HN50"/>
+  <dimension ref="A1:HP50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1522,6 +1522,16 @@
           <t>2025-12</t>
         </is>
       </c>
+      <c r="HO1" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="HP1" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2200,6 +2210,10 @@
       <c r="HN2" t="n">
         <v>0</v>
       </c>
+      <c r="HO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2878,6 +2892,10 @@
       <c r="HN3" t="n">
         <v>0</v>
       </c>
+      <c r="HO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3556,6 +3574,10 @@
       <c r="HN4" t="n">
         <v>177.923</v>
       </c>
+      <c r="HO4" t="n">
+        <v>187.498</v>
+      </c>
+      <c r="HP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4018,6 +4040,10 @@
       <c r="HN5" t="n">
         <v>118.64</v>
       </c>
+      <c r="HO5" t="n">
+        <v>114.407</v>
+      </c>
+      <c r="HP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4696,6 +4722,10 @@
       <c r="HN6" t="n">
         <v>0</v>
       </c>
+      <c r="HO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5374,6 +5404,10 @@
       <c r="HN7" t="n">
         <v>278.733</v>
       </c>
+      <c r="HO7" t="n">
+        <v>252.838</v>
+      </c>
+      <c r="HP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -6052,6 +6086,10 @@
       <c r="HN8" t="n">
         <v>252.838</v>
       </c>
+      <c r="HO8" t="n">
+        <v>219.825</v>
+      </c>
+      <c r="HP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -6730,6 +6768,10 @@
       <c r="HN9" t="n">
         <v>25.895</v>
       </c>
+      <c r="HO9" t="n">
+        <v>33.013</v>
+      </c>
+      <c r="HP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7408,6 +7450,10 @@
       <c r="HN10" t="n">
         <v>203.819</v>
       </c>
+      <c r="HO10" t="n">
+        <v>220.511</v>
+      </c>
+      <c r="HP10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7870,6 +7916,10 @@
       <c r="HN11" t="n">
         <v>200.074</v>
       </c>
+      <c r="HO11" t="n">
+        <v>220.083</v>
+      </c>
+      <c r="HP11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8548,6 +8598,10 @@
       <c r="HN12" t="n">
         <v>0</v>
       </c>
+      <c r="HO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9226,6 +9280,10 @@
       <c r="HN13" t="n">
         <v>139.961</v>
       </c>
+      <c r="HO13" t="n">
+        <v>145.373</v>
+      </c>
+      <c r="HP13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9904,6 +9962,10 @@
       <c r="HN14" t="n">
         <v>59.913</v>
       </c>
+      <c r="HO14" t="n">
+        <v>74.51000000000001</v>
+      </c>
+      <c r="HP14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10366,6 +10428,10 @@
       <c r="HN15" t="n">
         <v>59.913</v>
       </c>
+      <c r="HO15" t="n">
+        <v>74.51000000000001</v>
+      </c>
+      <c r="HP15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -11044,6 +11110,10 @@
       <c r="HN16" t="n">
         <v>0.2</v>
       </c>
+      <c r="HO16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="HP16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11506,6 +11576,10 @@
       <c r="HN17" t="n">
         <v>3.745</v>
       </c>
+      <c r="HO17" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="HP17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12184,6 +12258,10 @@
       <c r="HN18" t="n">
         <v>0</v>
       </c>
+      <c r="HO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12862,6 +12940,10 @@
       <c r="HN19" t="n">
         <v>4.029</v>
       </c>
+      <c r="HO19" t="n">
+        <v>3.268</v>
+      </c>
+      <c r="HP19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -13540,6 +13622,10 @@
       <c r="HN20" t="n">
         <v>0</v>
       </c>
+      <c r="HO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14218,6 +14304,10 @@
       <c r="HN21" t="n">
         <v>0</v>
       </c>
+      <c r="HO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14896,6 +14986,10 @@
       <c r="HN22" t="n">
         <v>0</v>
       </c>
+      <c r="HO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15574,6 +15668,10 @@
       <c r="HN23" t="n">
         <v>0</v>
       </c>
+      <c r="HO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16252,6 +16350,10 @@
       <c r="HN24" t="n">
         <v>4.029</v>
       </c>
+      <c r="HO24" t="n">
+        <v>3.268</v>
+      </c>
+      <c r="HP24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -16930,6 +17032,10 @@
       <c r="HN25" t="n">
         <v>0</v>
       </c>
+      <c r="HO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -17608,6 +17714,10 @@
       <c r="HN26" t="n">
         <v>107.81</v>
       </c>
+      <c r="HO26" t="n">
+        <v>103.393</v>
+      </c>
+      <c r="HP26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -18286,6 +18396,10 @@
       <c r="HN27" t="n">
         <v>103.114</v>
       </c>
+      <c r="HO27" t="n">
+        <v>93.08199999999999</v>
+      </c>
+      <c r="HP27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -18748,6 +18862,10 @@
       <c r="HN28" t="n">
         <v>0</v>
       </c>
+      <c r="HO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -19426,6 +19544,10 @@
       <c r="HN29" t="n">
         <v>0</v>
       </c>
+      <c r="HO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -20104,6 +20226,10 @@
       <c r="HN30" t="n">
         <v>46.113</v>
       </c>
+      <c r="HO30" t="n">
+        <v>70.413</v>
+      </c>
+      <c r="HP30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -20782,6 +20908,10 @@
       <c r="HN31" t="n">
         <v>70.413</v>
       </c>
+      <c r="HO31" t="n">
+        <v>83.121</v>
+      </c>
+      <c r="HP31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -21460,6 +21590,10 @@
       <c r="HN32" t="n">
         <v>-24.3</v>
       </c>
+      <c r="HO32" t="n">
+        <v>-12.708</v>
+      </c>
+      <c r="HP32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -22138,6 +22272,10 @@
       <c r="HN33" t="n">
         <v>186.624</v>
       </c>
+      <c r="HO33" t="n">
+        <v>183.767</v>
+      </c>
+      <c r="HP33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -22816,6 +22954,10 @@
       <c r="HN34" t="n">
         <v>182.503</v>
       </c>
+      <c r="HO34" t="n">
+        <v>178.381</v>
+      </c>
+      <c r="HP34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -23494,6 +23636,10 @@
       <c r="HN35" t="n">
         <v>0</v>
       </c>
+      <c r="HO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -24172,6 +24318,10 @@
       <c r="HN36" t="n">
         <v>0</v>
       </c>
+      <c r="HO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -24850,6 +25000,10 @@
       <c r="HN37" t="n">
         <v>0</v>
       </c>
+      <c r="HO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -25312,6 +25466,8 @@
       <c r="HL38" t="inlineStr"/>
       <c r="HM38" t="inlineStr"/>
       <c r="HN38" t="inlineStr"/>
+      <c r="HO38" t="inlineStr"/>
+      <c r="HP38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -25774,6 +25930,8 @@
       <c r="HL39" t="inlineStr"/>
       <c r="HM39" t="inlineStr"/>
       <c r="HN39" t="inlineStr"/>
+      <c r="HO39" t="inlineStr"/>
+      <c r="HP39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -26452,6 +26610,10 @@
       <c r="HN40" t="n">
         <v>0</v>
       </c>
+      <c r="HO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -27130,6 +27292,10 @@
       <c r="HN41" t="n">
         <v>0</v>
       </c>
+      <c r="HO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -27808,6 +27974,10 @@
       <c r="HN42" t="n">
         <v>0</v>
       </c>
+      <c r="HO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -28270,6 +28440,10 @@
       <c r="HN43" t="n">
         <v>0</v>
       </c>
+      <c r="HO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -28732,6 +28906,10 @@
       <c r="HN44" t="n">
         <v>0</v>
       </c>
+      <c r="HO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -29194,6 +29372,10 @@
       <c r="HN45" t="n">
         <v>0</v>
       </c>
+      <c r="HO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -29656,6 +29838,10 @@
       <c r="HN46" t="n">
         <v>0</v>
       </c>
+      <c r="HO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -30118,6 +30304,10 @@
       <c r="HN47" t="n">
         <v>0</v>
       </c>
+      <c r="HO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -30580,6 +30770,10 @@
       <c r="HN48" t="n">
         <v>0</v>
       </c>
+      <c r="HO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -31042,6 +31236,10 @@
       <c r="HN49" t="n">
         <v>0</v>
       </c>
+      <c r="HO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -31504,6 +31702,10 @@
       <c r="HN50" t="n">
         <v>0</v>
       </c>
+      <c r="HO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/services/data_raw/eurostat/AT_coal_NRG_CB_SFFM.xlsx
+++ b/services/data_raw/eurostat/AT_coal_NRG_CB_SFFM.xlsx
@@ -2213,7 +2213,9 @@
       <c r="HO2" t="n">
         <v>0</v>
       </c>
-      <c r="HP2" t="inlineStr"/>
+      <c r="HP2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2895,7 +2897,9 @@
       <c r="HO3" t="n">
         <v>0</v>
       </c>
-      <c r="HP3" t="inlineStr"/>
+      <c r="HP3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3577,7 +3581,9 @@
       <c r="HO4" t="n">
         <v>187.498</v>
       </c>
-      <c r="HP4" t="inlineStr"/>
+      <c r="HP4" t="n">
+        <v>194.768</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4043,7 +4049,9 @@
       <c r="HO5" t="n">
         <v>114.407</v>
       </c>
-      <c r="HP5" t="inlineStr"/>
+      <c r="HP5" t="n">
+        <v>110.797</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4725,7 +4733,9 @@
       <c r="HO6" t="n">
         <v>0</v>
       </c>
-      <c r="HP6" t="inlineStr"/>
+      <c r="HP6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5407,7 +5417,9 @@
       <c r="HO7" t="n">
         <v>252.838</v>
       </c>
-      <c r="HP7" t="inlineStr"/>
+      <c r="HP7" t="n">
+        <v>219.825</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -6089,7 +6101,9 @@
       <c r="HO8" t="n">
         <v>219.825</v>
       </c>
-      <c r="HP8" t="inlineStr"/>
+      <c r="HP8" t="n">
+        <v>226.969</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -6771,7 +6785,9 @@
       <c r="HO9" t="n">
         <v>33.013</v>
       </c>
-      <c r="HP9" t="inlineStr"/>
+      <c r="HP9" t="n">
+        <v>-7.144</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7453,7 +7469,9 @@
       <c r="HO10" t="n">
         <v>220.511</v>
       </c>
-      <c r="HP10" t="inlineStr"/>
+      <c r="HP10" t="n">
+        <v>187.624</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7919,7 +7937,9 @@
       <c r="HO11" t="n">
         <v>220.083</v>
       </c>
-      <c r="HP11" t="inlineStr"/>
+      <c r="HP11" t="n">
+        <v>187.547</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8601,7 +8621,9 @@
       <c r="HO12" t="n">
         <v>0</v>
       </c>
-      <c r="HP12" t="inlineStr"/>
+      <c r="HP12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9283,7 +9305,9 @@
       <c r="HO13" t="n">
         <v>145.373</v>
       </c>
-      <c r="HP13" t="inlineStr"/>
+      <c r="HP13" t="n">
+        <v>131.628</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9965,7 +9989,9 @@
       <c r="HO14" t="n">
         <v>74.51000000000001</v>
       </c>
-      <c r="HP14" t="inlineStr"/>
+      <c r="HP14" t="n">
+        <v>55.719</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10431,7 +10457,9 @@
       <c r="HO15" t="n">
         <v>74.51000000000001</v>
       </c>
-      <c r="HP15" t="inlineStr"/>
+      <c r="HP15" t="n">
+        <v>55.719</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -11113,7 +11141,9 @@
       <c r="HO16" t="n">
         <v>0.2</v>
       </c>
-      <c r="HP16" t="inlineStr"/>
+      <c r="HP16" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11579,7 +11609,9 @@
       <c r="HO17" t="n">
         <v>0.428</v>
       </c>
-      <c r="HP17" t="inlineStr"/>
+      <c r="HP17" t="n">
+        <v>0.077</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12261,7 +12293,9 @@
       <c r="HO18" t="n">
         <v>0</v>
       </c>
-      <c r="HP18" t="inlineStr"/>
+      <c r="HP18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12943,7 +12977,9 @@
       <c r="HO19" t="n">
         <v>3.268</v>
       </c>
-      <c r="HP19" t="inlineStr"/>
+      <c r="HP19" t="n">
+        <v>2.484</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -13625,7 +13661,9 @@
       <c r="HO20" t="n">
         <v>0</v>
       </c>
-      <c r="HP20" t="inlineStr"/>
+      <c r="HP20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14307,7 +14345,9 @@
       <c r="HO21" t="n">
         <v>0</v>
       </c>
-      <c r="HP21" t="inlineStr"/>
+      <c r="HP21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14989,7 +15029,9 @@
       <c r="HO22" t="n">
         <v>0</v>
       </c>
-      <c r="HP22" t="inlineStr"/>
+      <c r="HP22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15671,7 +15713,9 @@
       <c r="HO23" t="n">
         <v>0</v>
       </c>
-      <c r="HP23" t="inlineStr"/>
+      <c r="HP23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16353,7 +16397,9 @@
       <c r="HO24" t="n">
         <v>3.268</v>
       </c>
-      <c r="HP24" t="inlineStr"/>
+      <c r="HP24" t="n">
+        <v>2.484</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -17035,7 +17081,9 @@
       <c r="HO25" t="n">
         <v>0</v>
       </c>
-      <c r="HP25" t="inlineStr"/>
+      <c r="HP25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -17717,7 +17765,9 @@
       <c r="HO26" t="n">
         <v>103.393</v>
       </c>
-      <c r="HP26" t="inlineStr"/>
+      <c r="HP26" t="n">
+        <v>94.01300000000001</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -18399,7 +18449,9 @@
       <c r="HO27" t="n">
         <v>93.08199999999999</v>
       </c>
-      <c r="HP27" t="inlineStr"/>
+      <c r="HP27" t="n">
+        <v>67.45699999999999</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -18865,7 +18917,9 @@
       <c r="HO28" t="n">
         <v>0</v>
       </c>
-      <c r="HP28" t="inlineStr"/>
+      <c r="HP28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -19547,7 +19601,9 @@
       <c r="HO29" t="n">
         <v>0</v>
       </c>
-      <c r="HP29" t="inlineStr"/>
+      <c r="HP29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -20229,7 +20285,9 @@
       <c r="HO30" t="n">
         <v>70.413</v>
       </c>
-      <c r="HP30" t="inlineStr"/>
+      <c r="HP30" t="n">
+        <v>83.121</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -20911,7 +20969,9 @@
       <c r="HO31" t="n">
         <v>83.121</v>
       </c>
-      <c r="HP31" t="inlineStr"/>
+      <c r="HP31" t="n">
+        <v>88.267</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -21593,7 +21653,9 @@
       <c r="HO32" t="n">
         <v>-12.708</v>
       </c>
-      <c r="HP32" t="inlineStr"/>
+      <c r="HP32" t="n">
+        <v>-5.146</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -22275,7 +22337,9 @@
       <c r="HO33" t="n">
         <v>183.767</v>
       </c>
-      <c r="HP33" t="inlineStr"/>
+      <c r="HP33" t="n">
+        <v>156.324</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -22957,7 +23021,9 @@
       <c r="HO34" t="n">
         <v>178.381</v>
       </c>
-      <c r="HP34" t="inlineStr"/>
+      <c r="HP34" t="n">
+        <v>154.068</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -23639,7 +23705,9 @@
       <c r="HO35" t="n">
         <v>0</v>
       </c>
-      <c r="HP35" t="inlineStr"/>
+      <c r="HP35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -24321,7 +24389,9 @@
       <c r="HO36" t="n">
         <v>0</v>
       </c>
-      <c r="HP36" t="inlineStr"/>
+      <c r="HP36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -25003,7 +25073,9 @@
       <c r="HO37" t="n">
         <v>0</v>
       </c>
-      <c r="HP37" t="inlineStr"/>
+      <c r="HP37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -26613,7 +26685,9 @@
       <c r="HO40" t="n">
         <v>0</v>
       </c>
-      <c r="HP40" t="inlineStr"/>
+      <c r="HP40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -27295,7 +27369,9 @@
       <c r="HO41" t="n">
         <v>0</v>
       </c>
-      <c r="HP41" t="inlineStr"/>
+      <c r="HP41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -27977,7 +28053,9 @@
       <c r="HO42" t="n">
         <v>0</v>
       </c>
-      <c r="HP42" t="inlineStr"/>
+      <c r="HP42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -28443,7 +28521,9 @@
       <c r="HO43" t="n">
         <v>0</v>
       </c>
-      <c r="HP43" t="inlineStr"/>
+      <c r="HP43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -28909,7 +28989,9 @@
       <c r="HO44" t="n">
         <v>0</v>
       </c>
-      <c r="HP44" t="inlineStr"/>
+      <c r="HP44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -29375,7 +29457,9 @@
       <c r="HO45" t="n">
         <v>0</v>
       </c>
-      <c r="HP45" t="inlineStr"/>
+      <c r="HP45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -29841,7 +29925,9 @@
       <c r="HO46" t="n">
         <v>0</v>
       </c>
-      <c r="HP46" t="inlineStr"/>
+      <c r="HP46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -30307,7 +30393,9 @@
       <c r="HO47" t="n">
         <v>0</v>
       </c>
-      <c r="HP47" t="inlineStr"/>
+      <c r="HP47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -30773,7 +30861,9 @@
       <c r="HO48" t="n">
         <v>0</v>
       </c>
-      <c r="HP48" t="inlineStr"/>
+      <c r="HP48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -31239,7 +31329,9 @@
       <c r="HO49" t="n">
         <v>0</v>
       </c>
-      <c r="HP49" t="inlineStr"/>
+      <c r="HP49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -31705,7 +31797,9 @@
       <c r="HO50" t="n">
         <v>0</v>
       </c>
-      <c r="HP50" t="inlineStr"/>
+      <c r="HP50" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/services/data_raw/eurostat/AT_coal_NRG_CB_SFFM.xlsx
+++ b/services/data_raw/eurostat/AT_coal_NRG_CB_SFFM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HP50"/>
+  <dimension ref="A1:HQ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1532,6 +1532,11 @@
           <t>2026-02</t>
         </is>
       </c>
+      <c r="HQ1" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2216,6 +2221,7 @@
       <c r="HP2" t="n">
         <v>0</v>
       </c>
+      <c r="HQ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2900,6 +2906,7 @@
       <c r="HP3" t="n">
         <v>0</v>
       </c>
+      <c r="HQ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3584,6 +3591,7 @@
       <c r="HP4" t="n">
         <v>194.768</v>
       </c>
+      <c r="HQ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4052,6 +4060,7 @@
       <c r="HP5" t="n">
         <v>110.797</v>
       </c>
+      <c r="HQ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4736,6 +4745,7 @@
       <c r="HP6" t="n">
         <v>0</v>
       </c>
+      <c r="HQ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5420,6 +5430,7 @@
       <c r="HP7" t="n">
         <v>219.825</v>
       </c>
+      <c r="HQ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -6104,6 +6115,7 @@
       <c r="HP8" t="n">
         <v>226.969</v>
       </c>
+      <c r="HQ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -6788,6 +6800,7 @@
       <c r="HP9" t="n">
         <v>-7.144</v>
       </c>
+      <c r="HQ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7472,6 +7485,7 @@
       <c r="HP10" t="n">
         <v>187.624</v>
       </c>
+      <c r="HQ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7940,6 +7954,7 @@
       <c r="HP11" t="n">
         <v>187.547</v>
       </c>
+      <c r="HQ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8624,6 +8639,7 @@
       <c r="HP12" t="n">
         <v>0</v>
       </c>
+      <c r="HQ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9308,6 +9324,7 @@
       <c r="HP13" t="n">
         <v>131.628</v>
       </c>
+      <c r="HQ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9992,6 +10009,7 @@
       <c r="HP14" t="n">
         <v>55.719</v>
       </c>
+      <c r="HQ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10460,6 +10478,7 @@
       <c r="HP15" t="n">
         <v>55.719</v>
       </c>
+      <c r="HQ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -11144,6 +11163,7 @@
       <c r="HP16" t="n">
         <v>0.2</v>
       </c>
+      <c r="HQ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11612,6 +11632,7 @@
       <c r="HP17" t="n">
         <v>0.077</v>
       </c>
+      <c r="HQ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12296,6 +12317,7 @@
       <c r="HP18" t="n">
         <v>0</v>
       </c>
+      <c r="HQ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12980,6 +13002,7 @@
       <c r="HP19" t="n">
         <v>2.484</v>
       </c>
+      <c r="HQ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -13664,6 +13687,7 @@
       <c r="HP20" t="n">
         <v>0</v>
       </c>
+      <c r="HQ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14348,6 +14372,7 @@
       <c r="HP21" t="n">
         <v>0</v>
       </c>
+      <c r="HQ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15032,6 +15057,7 @@
       <c r="HP22" t="n">
         <v>0</v>
       </c>
+      <c r="HQ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15716,6 +15742,7 @@
       <c r="HP23" t="n">
         <v>0</v>
       </c>
+      <c r="HQ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16400,6 +16427,7 @@
       <c r="HP24" t="n">
         <v>2.484</v>
       </c>
+      <c r="HQ24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -17084,6 +17112,7 @@
       <c r="HP25" t="n">
         <v>0</v>
       </c>
+      <c r="HQ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -17768,6 +17797,7 @@
       <c r="HP26" t="n">
         <v>94.01300000000001</v>
       </c>
+      <c r="HQ26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -18452,6 +18482,7 @@
       <c r="HP27" t="n">
         <v>67.45699999999999</v>
       </c>
+      <c r="HQ27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -18920,6 +18951,7 @@
       <c r="HP28" t="n">
         <v>0</v>
       </c>
+      <c r="HQ28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -19604,6 +19636,7 @@
       <c r="HP29" t="n">
         <v>0</v>
       </c>
+      <c r="HQ29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -20288,6 +20321,7 @@
       <c r="HP30" t="n">
         <v>83.121</v>
       </c>
+      <c r="HQ30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -20972,6 +21006,7 @@
       <c r="HP31" t="n">
         <v>88.267</v>
       </c>
+      <c r="HQ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -21656,6 +21691,7 @@
       <c r="HP32" t="n">
         <v>-5.146</v>
       </c>
+      <c r="HQ32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -22340,6 +22376,7 @@
       <c r="HP33" t="n">
         <v>156.324</v>
       </c>
+      <c r="HQ33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -23024,6 +23061,7 @@
       <c r="HP34" t="n">
         <v>154.068</v>
       </c>
+      <c r="HQ34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -23708,6 +23746,7 @@
       <c r="HP35" t="n">
         <v>0</v>
       </c>
+      <c r="HQ35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -24392,6 +24431,7 @@
       <c r="HP36" t="n">
         <v>0</v>
       </c>
+      <c r="HQ36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -25076,6 +25116,7 @@
       <c r="HP37" t="n">
         <v>0</v>
       </c>
+      <c r="HQ37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -25540,6 +25581,7 @@
       <c r="HN38" t="inlineStr"/>
       <c r="HO38" t="inlineStr"/>
       <c r="HP38" t="inlineStr"/>
+      <c r="HQ38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -26004,6 +26046,7 @@
       <c r="HN39" t="inlineStr"/>
       <c r="HO39" t="inlineStr"/>
       <c r="HP39" t="inlineStr"/>
+      <c r="HQ39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -26688,6 +26731,7 @@
       <c r="HP40" t="n">
         <v>0</v>
       </c>
+      <c r="HQ40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -27372,6 +27416,7 @@
       <c r="HP41" t="n">
         <v>0</v>
       </c>
+      <c r="HQ41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -28056,6 +28101,7 @@
       <c r="HP42" t="n">
         <v>0</v>
       </c>
+      <c r="HQ42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -28524,6 +28570,7 @@
       <c r="HP43" t="n">
         <v>0</v>
       </c>
+      <c r="HQ43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -28992,6 +29039,7 @@
       <c r="HP44" t="n">
         <v>0</v>
       </c>
+      <c r="HQ44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -29460,6 +29508,7 @@
       <c r="HP45" t="n">
         <v>0</v>
       </c>
+      <c r="HQ45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -29928,6 +29977,7 @@
       <c r="HP46" t="n">
         <v>0</v>
       </c>
+      <c r="HQ46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -30396,6 +30446,7 @@
       <c r="HP47" t="n">
         <v>0</v>
       </c>
+      <c r="HQ47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -30864,6 +30915,7 @@
       <c r="HP48" t="n">
         <v>0</v>
       </c>
+      <c r="HQ48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -31332,6 +31384,7 @@
       <c r="HP49" t="n">
         <v>0</v>
       </c>
+      <c r="HQ49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -31800,6 +31853,7 @@
       <c r="HP50" t="n">
         <v>0</v>
       </c>
+      <c r="HQ50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/services/data_raw/eurostat/AT_coal_NRG_CB_SFFM.xlsx
+++ b/services/data_raw/eurostat/AT_coal_NRG_CB_SFFM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HQ50"/>
+  <dimension ref="A1:HS50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1537,6 +1537,16 @@
           <t>2026-03</t>
         </is>
       </c>
+      <c r="HR1" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="HS1" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2221,7 +2231,15 @@
       <c r="HP2" t="n">
         <v>0</v>
       </c>
-      <c r="HQ2" t="inlineStr"/>
+      <c r="HQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2906,7 +2924,15 @@
       <c r="HP3" t="n">
         <v>0</v>
       </c>
-      <c r="HQ3" t="inlineStr"/>
+      <c r="HQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3591,7 +3617,15 @@
       <c r="HP4" t="n">
         <v>194.768</v>
       </c>
-      <c r="HQ4" t="inlineStr"/>
+      <c r="HQ4" t="n">
+        <v>192.51</v>
+      </c>
+      <c r="HR4" t="n">
+        <v>203.712</v>
+      </c>
+      <c r="HS4" t="n">
+        <v>201.081</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4060,7 +4094,15 @@
       <c r="HP5" t="n">
         <v>110.797</v>
       </c>
-      <c r="HQ5" t="inlineStr"/>
+      <c r="HQ5" t="n">
+        <v>99.827</v>
+      </c>
+      <c r="HR5" t="n">
+        <v>122.682</v>
+      </c>
+      <c r="HS5" t="n">
+        <v>114.722</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4745,7 +4787,15 @@
       <c r="HP6" t="n">
         <v>0</v>
       </c>
-      <c r="HQ6" t="inlineStr"/>
+      <c r="HQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5430,7 +5480,15 @@
       <c r="HP7" t="n">
         <v>219.825</v>
       </c>
-      <c r="HQ7" t="inlineStr"/>
+      <c r="HQ7" t="n">
+        <v>226.969</v>
+      </c>
+      <c r="HR7" t="n">
+        <v>207.967</v>
+      </c>
+      <c r="HS7" t="n">
+        <v>203.462</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -6115,7 +6173,15 @@
       <c r="HP8" t="n">
         <v>226.969</v>
       </c>
-      <c r="HQ8" t="inlineStr"/>
+      <c r="HQ8" t="n">
+        <v>207.967</v>
+      </c>
+      <c r="HR8" t="n">
+        <v>203.462</v>
+      </c>
+      <c r="HS8" t="n">
+        <v>194.221</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -6800,7 +6866,15 @@
       <c r="HP9" t="n">
         <v>-7.144</v>
       </c>
-      <c r="HQ9" t="inlineStr"/>
+      <c r="HQ9" t="n">
+        <v>19.002</v>
+      </c>
+      <c r="HR9" t="n">
+        <v>4.505</v>
+      </c>
+      <c r="HS9" t="n">
+        <v>9.241</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7485,7 +7559,15 @@
       <c r="HP10" t="n">
         <v>187.624</v>
       </c>
-      <c r="HQ10" t="inlineStr"/>
+      <c r="HQ10" t="n">
+        <v>211.512</v>
+      </c>
+      <c r="HR10" t="n">
+        <v>208.217</v>
+      </c>
+      <c r="HS10" t="n">
+        <v>210.322</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7954,7 +8036,15 @@
       <c r="HP11" t="n">
         <v>187.547</v>
       </c>
-      <c r="HQ11" t="inlineStr"/>
+      <c r="HQ11" t="n">
+        <v>212.983</v>
+      </c>
+      <c r="HR11" t="n">
+        <v>206.102</v>
+      </c>
+      <c r="HS11" t="n">
+        <v>206.534</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8639,7 +8729,15 @@
       <c r="HP12" t="n">
         <v>0</v>
       </c>
-      <c r="HQ12" t="inlineStr"/>
+      <c r="HQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9324,7 +9422,15 @@
       <c r="HP13" t="n">
         <v>131.628</v>
       </c>
-      <c r="HQ13" t="inlineStr"/>
+      <c r="HQ13" t="n">
+        <v>143.085</v>
+      </c>
+      <c r="HR13" t="n">
+        <v>139.064</v>
+      </c>
+      <c r="HS13" t="n">
+        <v>143.157</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10009,7 +10115,15 @@
       <c r="HP14" t="n">
         <v>55.719</v>
       </c>
-      <c r="HQ14" t="inlineStr"/>
+      <c r="HQ14" t="n">
+        <v>69.69799999999999</v>
+      </c>
+      <c r="HR14" t="n">
+        <v>66.83799999999999</v>
+      </c>
+      <c r="HS14" t="n">
+        <v>63.178</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10478,7 +10592,15 @@
       <c r="HP15" t="n">
         <v>55.719</v>
       </c>
-      <c r="HQ15" t="inlineStr"/>
+      <c r="HQ15" t="n">
+        <v>69.69799999999999</v>
+      </c>
+      <c r="HR15" t="n">
+        <v>66.83799999999999</v>
+      </c>
+      <c r="HS15" t="n">
+        <v>63.178</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -11163,7 +11285,15 @@
       <c r="HP16" t="n">
         <v>0.2</v>
       </c>
-      <c r="HQ16" t="inlineStr"/>
+      <c r="HQ16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="HR16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="HS16" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11632,7 +11762,15 @@
       <c r="HP17" t="n">
         <v>0.077</v>
       </c>
-      <c r="HQ17" t="inlineStr"/>
+      <c r="HQ17" t="n">
+        <v>-1.471</v>
+      </c>
+      <c r="HR17" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="HS17" t="n">
+        <v>3.788</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12317,7 +12455,15 @@
       <c r="HP18" t="n">
         <v>0</v>
       </c>
-      <c r="HQ18" t="inlineStr"/>
+      <c r="HQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -13002,7 +13148,15 @@
       <c r="HP19" t="n">
         <v>2.484</v>
       </c>
-      <c r="HQ19" t="inlineStr"/>
+      <c r="HQ19" t="n">
+        <v>1.661</v>
+      </c>
+      <c r="HR19" t="n">
+        <v>2.258</v>
+      </c>
+      <c r="HS19" t="n">
+        <v>2.359</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -13687,7 +13841,15 @@
       <c r="HP20" t="n">
         <v>0</v>
       </c>
-      <c r="HQ20" t="inlineStr"/>
+      <c r="HQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14372,7 +14534,15 @@
       <c r="HP21" t="n">
         <v>0</v>
       </c>
-      <c r="HQ21" t="inlineStr"/>
+      <c r="HQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15057,7 +15227,15 @@
       <c r="HP22" t="n">
         <v>0</v>
       </c>
-      <c r="HQ22" t="inlineStr"/>
+      <c r="HQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15742,7 +15920,15 @@
       <c r="HP23" t="n">
         <v>0</v>
       </c>
-      <c r="HQ23" t="inlineStr"/>
+      <c r="HQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16427,7 +16613,15 @@
       <c r="HP24" t="n">
         <v>2.484</v>
       </c>
-      <c r="HQ24" t="inlineStr"/>
+      <c r="HQ24" t="n">
+        <v>1.661</v>
+      </c>
+      <c r="HR24" t="n">
+        <v>2.258</v>
+      </c>
+      <c r="HS24" t="n">
+        <v>2.359</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -17112,7 +17306,15 @@
       <c r="HP25" t="n">
         <v>0</v>
       </c>
-      <c r="HQ25" t="inlineStr"/>
+      <c r="HQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -17797,7 +17999,15 @@
       <c r="HP26" t="n">
         <v>94.01300000000001</v>
       </c>
-      <c r="HQ26" t="inlineStr"/>
+      <c r="HQ26" t="n">
+        <v>103.111</v>
+      </c>
+      <c r="HR26" t="n">
+        <v>101.757</v>
+      </c>
+      <c r="HS26" t="n">
+        <v>104.817</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -18482,7 +18692,15 @@
       <c r="HP27" t="n">
         <v>67.45699999999999</v>
       </c>
-      <c r="HQ27" t="inlineStr"/>
+      <c r="HQ27" t="n">
+        <v>71.797</v>
+      </c>
+      <c r="HR27" t="n">
+        <v>83.886</v>
+      </c>
+      <c r="HS27" t="n">
+        <v>75.883</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -18951,7 +19169,15 @@
       <c r="HP28" t="n">
         <v>0</v>
       </c>
-      <c r="HQ28" t="inlineStr"/>
+      <c r="HQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -19636,7 +19862,15 @@
       <c r="HP29" t="n">
         <v>0</v>
       </c>
-      <c r="HQ29" t="inlineStr"/>
+      <c r="HQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -20321,7 +20555,15 @@
       <c r="HP30" t="n">
         <v>83.121</v>
       </c>
-      <c r="HQ30" t="inlineStr"/>
+      <c r="HQ30" t="n">
+        <v>88.267</v>
+      </c>
+      <c r="HR30" t="n">
+        <v>76.01600000000001</v>
+      </c>
+      <c r="HS30" t="n">
+        <v>79.02800000000001</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -21006,7 +21248,15 @@
       <c r="HP31" t="n">
         <v>88.267</v>
       </c>
-      <c r="HQ31" t="inlineStr"/>
+      <c r="HQ31" t="n">
+        <v>76.01600000000001</v>
+      </c>
+      <c r="HR31" t="n">
+        <v>79.02800000000001</v>
+      </c>
+      <c r="HS31" t="n">
+        <v>73.81399999999999</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -21691,7 +21941,15 @@
       <c r="HP32" t="n">
         <v>-5.146</v>
       </c>
-      <c r="HQ32" t="inlineStr"/>
+      <c r="HQ32" t="n">
+        <v>12.251</v>
+      </c>
+      <c r="HR32" t="n">
+        <v>-3.012</v>
+      </c>
+      <c r="HS32" t="n">
+        <v>5.215</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -22376,7 +22634,15 @@
       <c r="HP33" t="n">
         <v>156.324</v>
       </c>
-      <c r="HQ33" t="inlineStr"/>
+      <c r="HQ33" t="n">
+        <v>187.158</v>
+      </c>
+      <c r="HR33" t="n">
+        <v>182.631</v>
+      </c>
+      <c r="HS33" t="n">
+        <v>185.914</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -23061,7 +23327,15 @@
       <c r="HP34" t="n">
         <v>154.068</v>
       </c>
-      <c r="HQ34" t="inlineStr"/>
+      <c r="HQ34" t="n">
+        <v>183.699</v>
+      </c>
+      <c r="HR34" t="n">
+        <v>176.919</v>
+      </c>
+      <c r="HS34" t="n">
+        <v>183.348</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -23746,7 +24020,15 @@
       <c r="HP35" t="n">
         <v>0</v>
       </c>
-      <c r="HQ35" t="inlineStr"/>
+      <c r="HQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -24431,7 +24713,15 @@
       <c r="HP36" t="n">
         <v>0</v>
       </c>
-      <c r="HQ36" t="inlineStr"/>
+      <c r="HQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -25116,7 +25406,15 @@
       <c r="HP37" t="n">
         <v>0</v>
       </c>
-      <c r="HQ37" t="inlineStr"/>
+      <c r="HQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -25582,6 +25880,8 @@
       <c r="HO38" t="inlineStr"/>
       <c r="HP38" t="inlineStr"/>
       <c r="HQ38" t="inlineStr"/>
+      <c r="HR38" t="inlineStr"/>
+      <c r="HS38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -26047,6 +26347,8 @@
       <c r="HO39" t="inlineStr"/>
       <c r="HP39" t="inlineStr"/>
       <c r="HQ39" t="inlineStr"/>
+      <c r="HR39" t="inlineStr"/>
+      <c r="HS39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -26731,7 +27033,15 @@
       <c r="HP40" t="n">
         <v>0</v>
       </c>
-      <c r="HQ40" t="inlineStr"/>
+      <c r="HQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -27416,7 +27726,15 @@
       <c r="HP41" t="n">
         <v>0</v>
       </c>
-      <c r="HQ41" t="inlineStr"/>
+      <c r="HQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -28101,7 +28419,15 @@
       <c r="HP42" t="n">
         <v>0</v>
       </c>
-      <c r="HQ42" t="inlineStr"/>
+      <c r="HQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -28570,7 +28896,15 @@
       <c r="HP43" t="n">
         <v>0</v>
       </c>
-      <c r="HQ43" t="inlineStr"/>
+      <c r="HQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -29039,7 +29373,15 @@
       <c r="HP44" t="n">
         <v>0</v>
       </c>
-      <c r="HQ44" t="inlineStr"/>
+      <c r="HQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -29508,7 +29850,15 @@
       <c r="HP45" t="n">
         <v>0</v>
       </c>
-      <c r="HQ45" t="inlineStr"/>
+      <c r="HQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -29977,7 +30327,15 @@
       <c r="HP46" t="n">
         <v>0</v>
       </c>
-      <c r="HQ46" t="inlineStr"/>
+      <c r="HQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -30446,7 +30804,15 @@
       <c r="HP47" t="n">
         <v>0</v>
       </c>
-      <c r="HQ47" t="inlineStr"/>
+      <c r="HQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -30915,7 +31281,15 @@
       <c r="HP48" t="n">
         <v>0</v>
       </c>
-      <c r="HQ48" t="inlineStr"/>
+      <c r="HQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR48" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -31384,7 +31758,15 @@
       <c r="HP49" t="n">
         <v>0</v>
       </c>
-      <c r="HQ49" t="inlineStr"/>
+      <c r="HQ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR49" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -31853,7 +32235,15 @@
       <c r="HP50" t="n">
         <v>0</v>
       </c>
-      <c r="HQ50" t="inlineStr"/>
+      <c r="HQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR50" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS50" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
